--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484616_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484616_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2146</v>
+        <v>3.1979</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2388</v>
+        <v>4.445</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0242</v>
+        <v>-1.2471</v>
       </c>
       <c r="G2" t="n">
         <v>4.1814</v>
@@ -610,13 +610,13 @@
         <v>1.4661</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0723</v>
+        <v>0.0556</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4419</v>
+        <v>-0.2356</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5142</v>
+        <v>0.2913</v>
       </c>
       <c r="V2" t="n">
         <v>-1.5889</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8587</v>
+        <v>1.4959</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4445</v>
+        <v>1.156</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4142</v>
+        <v>0.3399</v>
       </c>
       <c r="G3" t="n">
         <v>0.6254999999999999</v>
@@ -688,13 +688,13 @@
         <v>0.5498</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6835</v>
+        <v>0.3207</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2557</v>
+        <v>-0.0328</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4278</v>
+        <v>0.3535</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3671</v>
+        <v>1.3765</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1989</v>
+        <v>2.7871</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8318</v>
+        <v>-1.4106</v>
       </c>
       <c r="G4" t="n">
         <v>0.4687</v>
@@ -766,13 +766,13 @@
         <v>1.6493</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3806</v>
+        <v>-0.3712</v>
       </c>
       <c r="T4" t="n">
-        <v>0.546</v>
+        <v>0.1343</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9266</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>1.4622</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0281</v>
+        <v>0.7477</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5641</v>
+        <v>-0.6463</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5923</v>
+        <v>1.3941</v>
       </c>
       <c r="G5" t="n">
         <v>1.5336</v>
@@ -844,13 +844,13 @@
         <v>1.6493</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0394</v>
+        <v>-0.3198</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0761</v>
+        <v>-0.1583</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0368</v>
+        <v>-0.1614</v>
       </c>
       <c r="V5" t="n">
         <v>0.6335</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. BAEZA CABRERA</t>
+          <t>L. RODRIGUEZ CAMPIÑA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8159</v>
+        <v>0.6502</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4567</v>
+        <v>0.6502</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6408</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1859</v>
+        <v>0.6502</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4393</v>
+        <v>0.6502</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3355</v>
+        <v>0.6502</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4925</v>
+        <v>0.6502</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.157</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1496</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0532</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0964</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2411</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0717</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1694</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4278</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9658</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3937</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPIÑA</t>
+          <t>J. ROIG MESA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6502</v>
+        <v>0.4806</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6502</v>
+        <v>0.852</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0.3714</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6502</v>
+        <v>0.7521</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6502</v>
+        <v>-0.2513</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.0034</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6502</v>
+        <v>0.8026</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6502</v>
+        <v>0.1517</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.6509</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0.0505</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.403</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.3525</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.2609</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.0494</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.2115</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.0821</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.0821</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. HOYAS PEREZ</t>
+          <t>H. BAEZA CABRERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3154</v>
+        <v>0.4087</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0775</v>
+        <v>1.4707</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7621</v>
+        <v>-1.062</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4026</v>
+        <v>0.1859</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4118</v>
+        <v>1.4393</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8145</v>
+        <v>-1.2534</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2977</v>
+        <v>1.3355</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6194</v>
+        <v>2.4925</v>
       </c>
       <c r="L8" t="n">
-        <v>1.917</v>
+        <v>-1.157</v>
       </c>
       <c r="M8" t="n">
-        <v>1.105</v>
+        <v>-1.1496</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2075</v>
+        <v>-1.0532</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8974</v>
+        <v>-0.0964</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1318</v>
+        <v>0.8339</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2202</v>
+        <v>0.0856</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9116</v>
+        <v>0.7483</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9554</v>
+        <v>-0.4278</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.9658</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9554</v>
+        <v>-1.3937</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ROIG MESA</t>
+          <t>D. HOYAS PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1106</v>
+        <v>0.2658</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5085</v>
+        <v>1.0775</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6191</v>
+        <v>-0.8116</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7521</v>
+        <v>2.4026</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2513</v>
+        <v>-0.4118</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0034</v>
+        <v>2.8145</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8026</v>
+        <v>1.2977</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1517</v>
+        <v>-0.6194</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6509</v>
+        <v>1.917</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0505</v>
+        <v>1.105</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.403</v>
+        <v>0.2075</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3525</v>
+        <v>0.8974</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3303</v>
+        <v>-1.1814</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2941</v>
+        <v>-0.2202</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0362</v>
+        <v>-0.9612000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0821</v>
+        <v>-0.9554</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0821</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3675</v>
+        <v>-0.8724</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6703</v>
+        <v>-0.423</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.4494</v>
       </c>
       <c r="G10" t="n">
         <v>-1.185</v>
@@ -1234,13 +1234,13 @@
         <v>0.3665</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4223</v>
+        <v>0.0728</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5143</v>
+        <v>-0.267</v>
       </c>
       <c r="U10" t="n">
-        <v>0.092</v>
+        <v>0.3397</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1267</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3672</v>
+        <v>-2.9439</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9353</v>
+        <v>-1.5367</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4319</v>
+        <v>-1.4072</v>
       </c>
       <c r="G11" t="n">
         <v>-4.1085</v>
@@ -1312,13 +1312,13 @@
         <v>1.6493</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1479</v>
+        <v>0.2754</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3506</v>
+        <v>0.0479</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2028</v>
+        <v>0.2275</v>
       </c>
       <c r="V11" t="n">
         <v>-0.7602</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.5172</v>
+        <v>-7.0938</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.0622</v>
+        <v>-5.6636</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.455</v>
+        <v>-1.4302</v>
       </c>
       <c r="G12" t="n">
         <v>-2.8587</v>
@@ -1390,13 +1390,13 @@
         <v>1.4661</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1924</v>
+        <v>-0.769</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8273</v>
+        <v>-0.4287</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3651</v>
+        <v>-0.3403</v>
       </c>
       <c r="V12" t="n">
         <v>-1.267</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.1125</v>
+        <v>-2.286799999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>3.343200000000002</v>
+        <v>4.1689</v>
       </c>
       <c r="F13" t="n">
         <v>-6.4555</v>
@@ -1468,13 +1468,13 @@
         <v>10.0792</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6478</v>
+        <v>-0.8221000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.8511</v>
+        <v>-1.0254</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2035</v>
+        <v>0.2034000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-4.112399999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.4275</v>
+        <v>8.491099999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>6.9748</v>
+        <v>7.4555</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4527</v>
+        <v>1.0355</v>
       </c>
       <c r="G14" t="n">
         <v>5.4032</v>
@@ -1546,13 +1546,13 @@
         <v>1.8326</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5096000000000001</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5165</v>
+        <v>-0.0358</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0069</v>
+        <v>0.5897</v>
       </c>
       <c r="V14" t="n">
         <v>2.5339</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.7156</v>
+        <v>4.7098</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8157</v>
+        <v>3.6234</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9</v>
+        <v>1.0864</v>
       </c>
       <c r="G15" t="n">
         <v>1.8937</v>
@@ -1624,13 +1624,13 @@
         <v>1.2828</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0394</v>
+        <v>-0.0453</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2398</v>
+        <v>-0.4321</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2004</v>
+        <v>0.3869</v>
       </c>
       <c r="V15" t="n">
         <v>1.5785</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4313</v>
+        <v>2.3672</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8033</v>
+        <v>1.6109</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6281</v>
+        <v>0.7563</v>
       </c>
       <c r="G16" t="n">
         <v>-0.3666</v>
@@ -1702,13 +1702,13 @@
         <v>1.8326</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8974</v>
+        <v>0.8333</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2896</v>
+        <v>0.0973</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6078</v>
+        <v>0.736</v>
       </c>
       <c r="V16" t="n">
         <v>1.9005</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9004</v>
+        <v>-1.2107</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0179</v>
+        <v>0.6333</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9183</v>
+        <v>-1.844</v>
       </c>
       <c r="G19" t="n">
         <v>-1.9484</v>
@@ -1936,13 +1936,13 @@
         <v>0.5498</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0925</v>
+        <v>0.7823</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9503</v>
+        <v>0.5656</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1423</v>
+        <v>0.2166</v>
       </c>
       <c r="V19" t="n">
         <v>0.3219</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SORIANO ZORIO</t>
+          <t>P. BAENA SANCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2155</v>
+        <v>-1.7326</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2987</v>
+        <v>-3.1704</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9167999999999999</v>
+        <v>1.4379</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1562</v>
+        <v>-0.3402</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-0.658</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2404</v>
+        <v>0.3178</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8387</v>
+        <v>-0.0939</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2075</v>
+        <v>-0.3159</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6312</v>
+        <v>0.222</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3175</v>
+        <v>-0.2463</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7083</v>
+        <v>-0.3421</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6092</v>
+        <v>0.0958</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1833</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R20" t="n">
-        <v>0.733</v>
+        <v>1.2828</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7575</v>
+        <v>0.0737</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4563</v>
+        <v>-0.3276</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3012</v>
+        <v>0.4014</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4933</v>
+        <v>-2.1655</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1803</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.313</v>
+        <v>-2.0814</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8697</v>
@@ -2092,13 +2092,13 @@
         <v>0.3665</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4011</v>
+        <v>-0.0733</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3303</v>
+        <v>-0.2342</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0708</v>
+        <v>0.1608</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5889</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. BAENA SANCHEZ</t>
+          <t>J. SORIANO ZORIO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8587</v>
+        <v>-2.3553</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0358</v>
+        <v>-1.5872</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1771</v>
+        <v>-0.7681</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3402</v>
+        <v>-2.1562</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.658</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3178</v>
+        <v>-1.2404</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0939</v>
+        <v>-0.8387</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3159</v>
+        <v>-0.2075</v>
       </c>
       <c r="L22" t="n">
-        <v>0.222</v>
+        <v>-0.6312</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2463</v>
+        <v>-1.3175</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3421</v>
+        <v>-0.7083</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0958</v>
+        <v>-0.6092</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.4661</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2828</v>
+        <v>0.733</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0524</v>
+        <v>0.6177</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.193</v>
+        <v>0.1678</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1406</v>
+        <v>0.4498</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. MATEO LAZARO</t>
+          <t>J. CARRERAS MUNOZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4812</v>
+        <v>-2.8927</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4989</v>
+        <v>-3.0509</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9823</v>
+        <v>0.1582</v>
       </c>
       <c r="G23" t="n">
-        <v>-6.1821</v>
+        <v>-2.1825</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.999</v>
+        <v>-0.9195</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1831</v>
+        <v>-1.263</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.5239</v>
+        <v>-1.6663</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.5335</v>
+        <v>-0.4676</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.9903</v>
+        <v>-1.1987</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6582</v>
+        <v>-0.5161</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4655</v>
+        <v>-0.4519</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1928</v>
+        <v>-0.0643</v>
       </c>
       <c r="P23" t="n">
-        <v>0.733</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6493</v>
+        <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>1.9679</v>
+        <v>-0.3437</v>
       </c>
       <c r="T23" t="n">
-        <v>1.0408</v>
+        <v>-0.4683</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9271</v>
+        <v>0.1246</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.9005</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.9005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. CARRERAS MUNOZ</t>
+          <t>J. MATEO LAZARO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6139</v>
+        <v>-4.2767</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2432</v>
+        <v>-3.0758</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3707</v>
+        <v>-1.2009</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.1825</v>
+        <v>-6.1821</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9195</v>
+        <v>-4.999</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.263</v>
+        <v>-1.1831</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.6663</v>
+        <v>-4.5239</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.4676</v>
+        <v>-3.5335</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.1987</v>
+        <v>-0.9903</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5161</v>
+        <v>-1.6582</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4519</v>
+        <v>-1.4655</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0643</v>
+        <v>-0.1928</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3665</v>
+        <v>0.733</v>
       </c>
       <c r="Q24" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5498</v>
+        <v>1.6493</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0649</v>
+        <v>1.1723</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6606</v>
+        <v>0.4638</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4043</v>
+        <v>0.7085</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.9005</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="25">
@@ -2359,31 +2359,31 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.1123</v>
+        <v>5.035500000000003</v>
       </c>
       <c r="E25" t="n">
-        <v>6.455699999999998</v>
+        <v>6.455600000000003</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.343199999999999</v>
+        <v>-1.4201</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.647900000000002</v>
+        <v>-2.647900000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3967000000000012</v>
+        <v>0.3967000000000018</v>
       </c>
       <c r="I25" t="n">
         <v>-3.0447</v>
       </c>
       <c r="J25" t="n">
-        <v>7.537000000000003</v>
+        <v>7.537</v>
       </c>
       <c r="K25" t="n">
         <v>8.014400000000002</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.4774000000000007</v>
+        <v>-0.4774000000000005</v>
       </c>
       <c r="M25" t="n">
         <v>-10.1847</v>
@@ -2395,7 +2395,7 @@
         <v>-2.5672</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.0001000000000000445</v>
+        <v>-0.0001000000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>-10.0793</v>
@@ -2404,16 +2404,16 @@
         <v>10.0792</v>
       </c>
       <c r="S25" t="n">
-        <v>1.6479</v>
+        <v>3.5709</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2031999999999999</v>
+        <v>-0.2035</v>
       </c>
       <c r="U25" t="n">
-        <v>1.8512</v>
+        <v>3.7743</v>
       </c>
       <c r="V25" t="n">
-        <v>4.1124</v>
+        <v>4.112400000000001</v>
       </c>
       <c r="W25" t="n">
         <v>9.2011</v>
